--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260730_205415.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260730_205415.xlsx
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260730_205415.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260730_205415.xlsx
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6560,7 +6560,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
